--- a/recommender-server/data/courses_list_2425.xlsx
+++ b/recommender-server/data/courses_list_2425.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\2. Secretariat\3. Studies Realization\AY 2024-2025\2. Teaching Units\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michelefischer/MA1P/SocialComputing/course-recommender/recommender-server/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D6523A1-EF32-4CB7-A96C-C7DB82DC20A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D7B595-1BF2-D140-B750-515D7BAEE4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9DA79EC3-1862-49B1-8ED9-B637051F4A05}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{9DA79EC3-1862-49B1-8ED9-B637051F4A05}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="535">
   <si>
     <t>Title</t>
   </si>
@@ -2062,12 +2062,228 @@
 ILIAS
 The course page in ILIAS can be found at https://ilias.unibe.ch/goto_ilias3_unibe_crs_3102266.html.</t>
   </si>
+  <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/fabrication-and-prototyping-in-the-learninglab/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/modeling-and-scaling-of-generative-ai-systems/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/multimodal-user-interfaces/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/user-centered-design/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/advanced-networking-and-future-internet/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/advanced-software-engineering/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/compiler-construction-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/concurrency-multi-core-programming-and-data-processing/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/distributed-algorithms/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/network-security/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/scientific-reading-in-computer-networks/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/scientific-reading-in-computer-networks-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/scientific-writing-in-computer-networks/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/scientific-writing-in-computer-networks-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-communication-and-distributed-systems/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-communication-and-distributed-systems-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-cryptography-and-data-security/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-distributed-learning-systems/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-foundations-of-dependable-systems-i/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-foundations-of-dependable-systems-ii/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-hot-topics-in-operating-systems/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-software-engineering/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-software-engineering-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/software-product-lines/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/systems-verification/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/cryptography/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/security-advanced-topics/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-cryptography-and-data-security-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/3d-geometry-processing/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/applied-optimization/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/computer-vision/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/deep-learning/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/design-and-graphics-programming-for-game-development/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/graph-based-pattern-recognition/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-affective-computing-for-empathic-behaviour-change/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-applied-optimization/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-chatbots-and-conversational-agents/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-computer-graphics-and-geometry-processing/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-explainable-ai-human-computer-interaction-meets-artificial-intelligence/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-human-computer-interaction-i/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-human-computer-interaction-ii/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-machine-learning-and-artificial-intelligence/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-machine-learning-and-artificial-intelligence-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-pattern-recognition/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-pattern-recognition-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/algorithm-design/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/automata-on-infinite-structures/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/machine-learning-theory-fairness-and-privacy/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/reinforcement-learning-and-decision-making-under-uncertainty/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-advanced-topics-in-reinforcement-learning-and-decision-making/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-logic-and-theoretical-computer-science-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/advanced-topics-in-decision-support/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/choice-based-optimization-and-its-application-to-revenue-management/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/design-of-governance-in-socio-technical-information-systems/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/fuzzy-sets-and-systems-i/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/fuzzy-sets-and-systems-ii/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/graph-theory-and-applications/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/introduction-to-recommender-systems/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/mathematical-modeling-and-linear-optimization/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-life-engineering/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-life-engineering-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-social-computing/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-urban-computing/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/big-data-infrastructures/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/data-management-data-structures/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/distributed-deep-learning-systems/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/pattern-recognition/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-data-science/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-geometry-and-topology-in-deep-learning/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/seminar-natural-language-processing-2/</t>
+  </si>
+  <si>
+    <t>https://mcs.unibnf.ch/courses/social-media-analytics/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2079,6 +2295,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2101,10 +2325,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2112,9 +2337,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2130,7 +2357,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2446,13 +2673,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48F83C5D-D3C4-4BD3-B986-C69CD42EEA8A}">
-  <dimension ref="A1:R72"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S72"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="38.5" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2507,22 +2735,25 @@
       <c r="R1" s="1" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>193</v>
@@ -2531,16 +2762,16 @@
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>323</v>
@@ -2552,33 +2783,30 @@
         <v>325</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>193</v>
@@ -2587,16 +2815,16 @@
         <v>5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>238</v>
+      <c r="J3" s="2">
+        <v>11072</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>323</v>
@@ -2605,33 +2833,30 @@
         <v>324</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="R3" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>192</v>
@@ -2643,16 +2868,16 @@
         <v>5</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>323</v>
@@ -2661,36 +2886,39 @@
         <v>324</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>326</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>193</v>
@@ -2699,16 +2927,16 @@
         <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J5" s="2">
-        <v>63021</v>
+        <v>53086</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>323</v>
@@ -2717,7 +2945,7 @@
         <v>324</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>337</v>
+        <v>408</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>326</v>
@@ -2725,28 +2953,28 @@
       <c r="P5" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="R5" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>193</v>
@@ -2755,16 +2983,16 @@
         <v>5</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>240</v>
+        <v>199</v>
+      </c>
+      <c r="J6" s="2">
+        <v>43124</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>323</v>
@@ -2773,30 +3001,33 @@
         <v>324</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>341</v>
+        <v>410</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>328</v>
+        <v>411</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>192</v>
@@ -2808,16 +3039,16 @@
         <v>5</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>323</v>
@@ -2826,33 +3057,36 @@
         <v>324</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>330</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>192</v>
@@ -2864,16 +3098,16 @@
         <v>5</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>323</v>
@@ -2882,33 +3116,36 @@
         <v>324</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>326</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>335</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>192</v>
@@ -2920,16 +3157,16 @@
         <v>5</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>243</v>
+      <c r="J9" s="2">
+        <v>63021</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>323</v>
@@ -2938,36 +3175,39 @@
         <v>324</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>326</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>328</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>193</v>
@@ -2976,13 +3216,13 @@
         <v>5</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>307</v>
@@ -2994,30 +3234,36 @@
         <v>324</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>326</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>328</v>
+        <v>368</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="C11" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>193</v>
@@ -3026,16 +3272,16 @@
         <v>5</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>323</v>
@@ -3044,33 +3290,30 @@
         <v>324</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>328</v>
+        <v>415</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>192</v>
@@ -3082,16 +3325,16 @@
         <v>5</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>323</v>
@@ -3100,36 +3343,39 @@
         <v>324</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>328</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>193</v>
@@ -3138,16 +3384,16 @@
         <v>5</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>208</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>323</v>
@@ -3156,7 +3402,7 @@
         <v>324</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>355</v>
@@ -3164,28 +3410,25 @@
       <c r="P13" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="Q13" s="2" t="s">
-        <v>335</v>
-      </c>
       <c r="R13" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>193</v>
@@ -3194,16 +3437,16 @@
         <v>5</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>323</v>
@@ -3212,36 +3455,33 @@
         <v>324</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="R14" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>419</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>193</v>
@@ -3250,16 +3490,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>323</v>
@@ -3268,36 +3508,36 @@
         <v>324</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>335</v>
+        <v>421</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>193</v>
@@ -3306,16 +3546,16 @@
         <v>5</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="J16" s="2">
-        <v>11113</v>
+      <c r="J16" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>323</v>
@@ -3324,36 +3564,33 @@
         <v>324</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>193</v>
@@ -3362,16 +3599,16 @@
         <v>5</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>323</v>
@@ -3380,36 +3617,36 @@
         <v>324</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>326</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>328</v>
+        <v>421</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>193</v>
@@ -3418,45 +3655,48 @@
         <v>5</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>372</v>
+        <v>425</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>426</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>192</v>
@@ -3468,48 +3708,57 @@
         <v>5</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>371</v>
+        <v>337</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>193</v>
@@ -3518,48 +3767,51 @@
         <v>5</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>428</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>192</v>
@@ -3571,48 +3823,54 @@
         <v>5</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>326</v>
       </c>
+      <c r="P21" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="Q21" s="2" t="s">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>192</v>
@@ -3624,16 +3882,16 @@
         <v>5</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>323</v>
@@ -3642,36 +3900,39 @@
         <v>324</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>193</v>
@@ -3680,16 +3941,16 @@
         <v>5</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>323</v>
@@ -3698,36 +3959,36 @@
         <v>324</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>372</v>
+        <v>430</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>193</v>
@@ -3736,16 +3997,16 @@
         <v>5</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>323</v>
@@ -3754,33 +4015,30 @@
         <v>324</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>381</v>
+        <v>333</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>372</v>
+        <v>415</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>432</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>192</v>
@@ -3792,51 +4050,57 @@
         <v>5</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="J25" s="2">
-        <v>63587</v>
+      <c r="J25" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>326</v>
       </c>
+      <c r="P25" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="Q25" s="2" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>193</v>
@@ -3845,16 +4109,16 @@
         <v>5</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>323</v>
@@ -3863,33 +4127,27 @@
         <v>324</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>384</v>
+        <v>433</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>372</v>
+        <v>434</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>192</v>
@@ -3901,48 +4159,54 @@
         <v>5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>326</v>
+        <v>355</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>192</v>
@@ -3954,48 +4218,54 @@
         <v>5</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>326</v>
       </c>
+      <c r="P28" s="2" t="s">
+        <v>334</v>
+      </c>
       <c r="Q28" s="2" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>192</v>
@@ -4007,16 +4277,16 @@
         <v>5</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>208</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>323</v>
@@ -4025,36 +4295,39 @@
         <v>324</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>372</v>
+        <v>335</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>193</v>
@@ -4063,48 +4336,51 @@
         <v>5</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>371</v>
+        <v>436</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="Q30" s="2" t="s">
-        <v>372</v>
+      <c r="P30" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>192</v>
@@ -4116,72 +4392,75 @@
         <v>5</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G32" s="2">
+        <v>5</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="2">
-        <v>5</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="J32" s="2" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>323</v>
@@ -4190,36 +4469,36 @@
         <v>324</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>394</v>
+        <v>337</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+        <v>432</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>97</v>
+        <v>161</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>193</v>
@@ -4228,16 +4507,16 @@
         <v>5</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>323</v>
@@ -4246,30 +4525,33 @@
         <v>324</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>100</v>
+        <v>52</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>192</v>
@@ -4281,54 +4563,51 @@
         <v>5</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="Q34" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>50</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>193</v>
@@ -4337,13 +4616,13 @@
         <v>5</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="J35" s="2">
-        <v>11593</v>
+      <c r="J35" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>300</v>
@@ -4352,36 +4631,33 @@
         <v>323</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="Q35" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>192</v>
@@ -4393,16 +4669,16 @@
         <v>5</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>323</v>
@@ -4413,28 +4689,28 @@
       <c r="N36" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="O36" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="Q36" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>194</v>
@@ -4446,48 +4722,51 @@
         <v>5</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>405</v>
+        <v>371</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>193</v>
@@ -4496,16 +4775,16 @@
         <v>5</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="J38" s="2">
-        <v>11072</v>
+        <v>208</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>323</v>
@@ -4514,27 +4793,36 @@
         <v>324</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>330</v>
+        <v>355</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>194</v>
@@ -4546,51 +4834,54 @@
         <v>5</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J39" s="2">
-        <v>53086</v>
+        <v>208</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>408</v>
+        <v>371</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>193</v>
@@ -4599,48 +4890,51 @@
         <v>5</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="J40" s="2">
-        <v>43124</v>
+      <c r="J40" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>411</v>
+        <v>326</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>194</v>
@@ -4652,16 +4946,16 @@
         <v>5</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>323</v>
@@ -4670,101 +4964,110 @@
         <v>324</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="O41" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G42" s="2">
+        <v>5</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="O42" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="R41" s="2" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G42" s="2">
-        <v>5</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="I42" s="2" t="s">
+      <c r="Q42" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G43" s="2">
+        <v>5</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I43" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K42" s="2" t="s">
+      <c r="J43" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G43" s="2">
-        <v>5</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>323</v>
@@ -4773,27 +5076,36 @@
         <v>324</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>361</v>
+        <v>331</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>129</v>
+        <v>64</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>194</v>
@@ -4805,16 +5117,16 @@
         <v>5</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>323</v>
@@ -4823,30 +5135,36 @@
         <v>324</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>337</v>
+        <v>377</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>330</v>
+        <v>448</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>193</v>
@@ -4855,16 +5173,16 @@
         <v>5</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>323</v>
@@ -4873,33 +5191,39 @@
         <v>324</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>420</v>
+        <v>379</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>421</v>
+        <v>331</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>193</v>
@@ -4908,16 +5232,16 @@
         <v>5</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>323</v>
@@ -4926,27 +5250,36 @@
         <v>324</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>405</v>
+        <v>330</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>194</v>
@@ -4958,16 +5291,16 @@
         <v>5</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>323</v>
@@ -4976,86 +5309,92 @@
         <v>324</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="O47" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G48" s="2">
+        <v>5</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J48" s="2">
+        <v>63587</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="O48" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P47" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G48" s="2">
-        <v>5</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>426</v>
+      <c r="Q48" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>193</v>
@@ -5070,10 +5409,10 @@
         <v>208</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>323</v>
@@ -5082,30 +5421,36 @@
         <v>324</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>355</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>428</v>
+        <v>385</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>194</v>
@@ -5117,51 +5462,54 @@
         <v>5</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>430</v>
+      <c r="Q50" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>193</v>
@@ -5170,45 +5518,51 @@
         <v>5</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>415</v>
+        <v>326</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>194</v>
@@ -5220,51 +5574,54 @@
         <v>5</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>433</v>
+        <v>371</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P52" s="2" t="s">
-        <v>434</v>
+      <c r="Q52" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>193</v>
@@ -5273,51 +5630,54 @@
         <v>5</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>436</v>
+        <v>371</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P53" s="2" t="s">
-        <v>421</v>
+      <c r="Q53" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>193</v>
@@ -5326,16 +5686,16 @@
         <v>5</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>323</v>
@@ -5344,83 +5704,92 @@
         <v>324</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="O54" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G55" s="2">
+        <v>5</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="O55" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="P54" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="R54" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G55" s="2">
-        <v>5</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>389</v>
+      <c r="Q55" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>194</v>
@@ -5432,51 +5801,54 @@
         <v>5</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="J56" s="2">
-        <v>63091</v>
+      <c r="J56" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>442</v>
+        <v>326</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>193</v>
@@ -5485,48 +5857,54 @@
         <v>5</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>333</v>
+        <v>371</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>326</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>338</v>
+        <v>392</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>194</v>
@@ -5538,16 +5916,16 @@
         <v>5</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>323</v>
@@ -5558,25 +5936,31 @@
       <c r="N58" s="2" t="s">
         <v>371</v>
       </c>
+      <c r="O58" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="Q58" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>55</v>
+        <v>185</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>56</v>
+        <v>186</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>194</v>
@@ -5588,48 +5972,54 @@
         <v>5</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>371</v>
+        <v>456</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>457</v>
       </c>
       <c r="Q59" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>169</v>
+        <v>93</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>193</v>
@@ -5638,48 +6028,54 @@
         <v>5</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>355</v>
+        <v>330</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="Q60" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>173</v>
+        <v>94</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>194</v>
@@ -5691,13 +6087,13 @@
         <v>5</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>301</v>
@@ -5709,7 +6105,7 @@
         <v>324</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>448</v>
@@ -5718,24 +6114,27 @@
         <v>372</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>193</v>
@@ -5744,16 +6143,16 @@
         <v>5</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>323</v>
@@ -5762,33 +6161,36 @@
         <v>324</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>448</v>
+        <v>341</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>193</v>
@@ -5797,16 +6199,16 @@
         <v>5</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>323</v>
@@ -5815,30 +6217,33 @@
         <v>324</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>448</v>
+        <v>341</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>176</v>
+        <v>99</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>194</v>
@@ -5850,13 +6255,13 @@
         <v>5</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>301</v>
@@ -5865,33 +6270,36 @@
         <v>323</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="Q64" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>194</v>
@@ -5903,16 +6311,16 @@
         <v>5</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>323</v>
@@ -5930,24 +6338,27 @@
         <v>372</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>180</v>
+        <v>101</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>193</v>
@@ -5956,48 +6367,54 @@
         <v>5</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>293</v>
+        <v>201</v>
+      </c>
+      <c r="J66" s="2">
+        <v>11593</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>402</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>194</v>
@@ -6009,51 +6426,54 @@
         <v>5</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>294</v>
+        <v>201</v>
+      </c>
+      <c r="J67" s="2">
+        <v>11610</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="Q67" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+      <c r="S67" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>184</v>
+        <v>104</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>193</v>
@@ -6062,48 +6482,51 @@
         <v>5</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>324</v>
+        <v>370</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>456</v>
+        <v>371</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>457</v>
+        <v>326</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>372</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>94</v>
+        <v>164</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>95</v>
+        <v>165</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>194</v>
@@ -6115,16 +6538,16 @@
         <v>5</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>296</v>
+        <v>199</v>
+      </c>
+      <c r="J69" s="2">
+        <v>63091</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>323</v>
@@ -6133,30 +6556,36 @@
         <v>324</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="Q69" s="2" t="s">
-        <v>372</v>
+        <v>441</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>442</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>100</v>
+        <v>45</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>193</v>
@@ -6165,16 +6594,16 @@
         <v>5</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="J70" s="2" t="s">
-        <v>297</v>
+      <c r="J70" s="2">
+        <v>11113</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>323</v>
@@ -6183,30 +6612,36 @@
         <v>324</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>399</v>
+        <v>358</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>415</v>
+        <v>330</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>194</v>
@@ -6218,51 +6653,54 @@
         <v>5</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>199</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>323</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="Q71" s="2" t="s">
-        <v>372</v>
+      <c r="P71" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>193</v>
@@ -6271,16 +6709,16 @@
         <v>5</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="J72" s="2">
-        <v>11610</v>
+        <v>199</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>250</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>323</v>
@@ -6289,19 +6727,101 @@
         <v>324</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>401</v>
+        <v>340</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>415</v>
+        <v>326</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>368</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>462</v>
+        <v>369</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S72">
+    <sortCondition ref="A2:A72"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="S21" r:id="rId1" xr:uid="{AA5539E2-6E4F-E34E-989C-C4A1B0D74809}"/>
+    <hyperlink ref="S29" r:id="rId2" xr:uid="{158CBA78-1FA3-E847-B3EC-A4B592CC0B97}"/>
+    <hyperlink ref="S30" r:id="rId3" xr:uid="{D976271E-C050-9F48-9DE5-9983EE9021C9}"/>
+    <hyperlink ref="S72" r:id="rId4" xr:uid="{8E34DC75-C257-494F-84D6-483C3AAF83A4}"/>
+    <hyperlink ref="S3" r:id="rId5" xr:uid="{C5042C79-A299-BA4E-AB0D-3B28AC8C1A48}"/>
+    <hyperlink ref="S4" r:id="rId6" xr:uid="{1DD8BB82-4FB1-B649-9798-B83666D94A70}"/>
+    <hyperlink ref="S11" r:id="rId7" xr:uid="{FE4808E9-6EA4-CD41-B41B-009C36B49360}"/>
+    <hyperlink ref="S13" r:id="rId8" xr:uid="{104A791C-E22C-5043-85D7-EAC9F385B41E}"/>
+    <hyperlink ref="S19" r:id="rId9" xr:uid="{B8DF5AFA-851D-6A44-A826-01E37F2E1A92}"/>
+    <hyperlink ref="S31" r:id="rId10" xr:uid="{8634AFD1-52DE-0A4A-B72A-D9286ECA8767}"/>
+    <hyperlink ref="S34" r:id="rId11" xr:uid="{38433F8C-5C05-F541-81CC-781B455F6EF4}"/>
+    <hyperlink ref="S35" r:id="rId12" xr:uid="{15D039AA-C3EC-EF41-B9DE-6653E287360A}"/>
+    <hyperlink ref="S36" r:id="rId13" xr:uid="{E086BF18-9E6A-2C42-B20A-675734B3E5EA}"/>
+    <hyperlink ref="S37" r:id="rId14" xr:uid="{99555DD2-3922-974A-8E0F-02F77F50C517}"/>
+    <hyperlink ref="S43" r:id="rId15" xr:uid="{F80D5F21-F6F8-654F-B371-F6500E660B7C}"/>
+    <hyperlink ref="S44" r:id="rId16" xr:uid="{B40B2D64-2A57-004B-864B-66738DCF1FFC}"/>
+    <hyperlink ref="S46" r:id="rId17" xr:uid="{8DE91294-B0EF-944E-B48A-D750CFB66BD9}"/>
+    <hyperlink ref="S49" r:id="rId18" xr:uid="{3A9BF2C8-5438-6A44-8FF3-6841F560A9F6}"/>
+    <hyperlink ref="S51" r:id="rId19" xr:uid="{23C24424-EC05-1546-AB1B-90A3D285D367}"/>
+    <hyperlink ref="S52" r:id="rId20" xr:uid="{3BB91743-528C-CE46-8CDB-C204C278E331}"/>
+    <hyperlink ref="S54" r:id="rId21" xr:uid="{FC4E90D8-4F2E-7C44-9381-1662350F9563}"/>
+    <hyperlink ref="S66" r:id="rId22" xr:uid="{EA9384EC-5C21-2340-A65F-7A8BEDA845C7}"/>
+    <hyperlink ref="S67" r:id="rId23" xr:uid="{72AFA8D2-32A8-2E48-9029-A0F0F214A457}"/>
+    <hyperlink ref="S70" r:id="rId24" xr:uid="{B9136F36-B685-A744-B676-6916FEC3365F}"/>
+    <hyperlink ref="S71" r:id="rId25" xr:uid="{A3D75D94-0719-B545-8E19-8D246693FD73}"/>
+    <hyperlink ref="S14" r:id="rId26" xr:uid="{7FFA3F0B-450F-0246-86D0-25F8427A1FA2}"/>
+    <hyperlink ref="S38" r:id="rId27" xr:uid="{0694322A-A1DA-AA4C-895F-76EC703D0499}"/>
+    <hyperlink ref="S47" r:id="rId28" xr:uid="{950DAB5A-3201-0E40-BA45-3FB9266FAB6A}"/>
+    <hyperlink ref="S2" r:id="rId29" xr:uid="{4DB2EF4E-8493-4E40-AD3F-6FFFF70B246C}"/>
+    <hyperlink ref="S7" r:id="rId30" xr:uid="{F8544E81-49FA-A247-9556-40017F4D4CC5}"/>
+    <hyperlink ref="S12" r:id="rId31" xr:uid="{EA3064D4-A563-1C49-85B4-5A9A62582A9B}"/>
+    <hyperlink ref="S16" r:id="rId32" xr:uid="{0779CE8A-297E-E845-B9B5-E85995997F5B}"/>
+    <hyperlink ref="S17" r:id="rId33" xr:uid="{B854C7DD-E60F-ED44-AF50-D10261880D50}"/>
+    <hyperlink ref="S24" r:id="rId34" xr:uid="{ACF3F08E-B603-2A40-9003-0C6DCFE8D018}"/>
+    <hyperlink ref="S40" r:id="rId35" xr:uid="{20FB0A78-C359-6843-80DB-427920159DA0}"/>
+    <hyperlink ref="S41" r:id="rId36" xr:uid="{313B1FF5-F771-6745-850D-1604A8DF5C2A}"/>
+    <hyperlink ref="S42" r:id="rId37" xr:uid="{9DFD2C06-CB92-364D-8371-3028274FA25F}"/>
+    <hyperlink ref="S45" r:id="rId38" xr:uid="{1488E8DA-FD3F-3640-9642-050C7F732C35}"/>
+    <hyperlink ref="S50" r:id="rId39" xr:uid="{B83F0F68-518A-5F42-AD13-DF1189A7F131}"/>
+    <hyperlink ref="S55" r:id="rId40" xr:uid="{B29E990F-4719-F042-B1F3-D1CDFD00D1E1}"/>
+    <hyperlink ref="S56" r:id="rId41" xr:uid="{E8502A7C-A45B-C94F-86BB-27E9F473408B}"/>
+    <hyperlink ref="S60" r:id="rId42" xr:uid="{3233BC8E-85EF-6540-A423-1AEA9E1C6A64}"/>
+    <hyperlink ref="S61" r:id="rId43" xr:uid="{2F4A735F-5337-434D-BB47-EB24C3D44DAB}"/>
+    <hyperlink ref="S63" r:id="rId44" xr:uid="{F9C3C708-68E7-664B-8CB1-34C72B5789DD}"/>
+    <hyperlink ref="S64" r:id="rId45" xr:uid="{B5E58710-9EDB-FF47-A8AA-DE50A1667AD0}"/>
+    <hyperlink ref="S6" r:id="rId46" xr:uid="{FF0DA8E1-C608-6D4F-B8D9-A7FC5757E1D3}"/>
+    <hyperlink ref="S8" r:id="rId47" xr:uid="{20862CC6-5CA6-7F44-8173-C2CF52C3F952}"/>
+    <hyperlink ref="S27" r:id="rId48" xr:uid="{09380E09-C3D9-DD43-A527-41FCE171EBA1}"/>
+    <hyperlink ref="S33" r:id="rId49" xr:uid="{ED9F3F40-EE0E-D54F-A947-38E1A8933C21}"/>
+    <hyperlink ref="S39" r:id="rId50" xr:uid="{D161D186-3D69-A949-866D-13F526B3FA79}"/>
+    <hyperlink ref="S59" r:id="rId51" xr:uid="{81D7331A-53C5-8D4F-86F8-D591EEA5D8F4}"/>
+    <hyperlink ref="S5" r:id="rId52" xr:uid="{F58722EB-2CEA-8240-AAF1-1EA04EA4EFDB}"/>
+    <hyperlink ref="S10" r:id="rId53" xr:uid="{20CEF982-2508-AD42-AC6F-0662EB300351}"/>
+    <hyperlink ref="S18" r:id="rId54" xr:uid="{4EE93EEC-F276-C745-9890-906827A8E6C8}"/>
+    <hyperlink ref="S22" r:id="rId55" xr:uid="{FDEA4086-8F0E-554E-9B96-3CDE2A0D8114}"/>
+    <hyperlink ref="S23" r:id="rId56" xr:uid="{5BF32223-8F66-414A-B75A-2FEC7193E6E6}"/>
+    <hyperlink ref="S25" r:id="rId57" xr:uid="{D01A4D3C-3022-A84C-911E-397C2272CDF8}"/>
+    <hyperlink ref="S26" r:id="rId58" xr:uid="{7B68F71F-80D3-0E4C-9943-37DF3DC3E690}"/>
+    <hyperlink ref="S28" r:id="rId59" xr:uid="{33D3B487-2DCA-5445-A40D-B0F8BDEECD92}"/>
+    <hyperlink ref="S57" r:id="rId60" xr:uid="{23321763-2F8B-7942-86AA-1B1293A2C520}"/>
+    <hyperlink ref="S58" r:id="rId61" xr:uid="{CF7E2F1F-8287-B741-98C0-879980D6626C}"/>
+    <hyperlink ref="S65" r:id="rId62" xr:uid="{8B6D0818-E559-1E44-8E47-387373107872}"/>
+    <hyperlink ref="S68" r:id="rId63" xr:uid="{FC088632-FB94-8842-8017-085309B04DF9}"/>
+    <hyperlink ref="S9" r:id="rId64" xr:uid="{F5DD23FE-57C9-E64F-8037-81B1E39589DF}"/>
+    <hyperlink ref="S15" r:id="rId65" xr:uid="{1A60609C-EB85-644E-8375-EAC711BEF316}"/>
+    <hyperlink ref="S20" r:id="rId66" xr:uid="{3EA7710E-0B8C-294F-BBBC-2494C508F676}"/>
+    <hyperlink ref="S32" r:id="rId67" xr:uid="{C2D1FA71-B72A-DB42-86FE-5854847BF1A9}"/>
+    <hyperlink ref="S48" r:id="rId68" xr:uid="{1F959AE8-F2B1-A643-B458-6E9E593278B2}"/>
+    <hyperlink ref="S53" r:id="rId69" xr:uid="{BA2FF1A8-2D4B-824C-86DE-C200C77D98AE}"/>
+    <hyperlink ref="S62" r:id="rId70" xr:uid="{315113A3-A745-2245-BFC7-3B905138CC4F}"/>
+    <hyperlink ref="S69" r:id="rId71" xr:uid="{62CEFAC6-6196-3547-BAA8-64C65017FD6C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>